--- a/diseases/d017/2005-2009.xlsx
+++ b/diseases/d017/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2149,9 +2140,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2693,9 +2681,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3137,9 +3122,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3681,9 +3663,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4125,9 +4104,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4669,9 +4645,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4965,9 +4938,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -5509,9 +5479,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5805,9 +5772,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6349,9 +6313,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -6645,9 +6606,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7189,9 +7147,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7485,9 +7440,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8029,9 +7981,6 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -8473,9 +8422,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9017,9 +8963,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -9313,9 +9256,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9857,9 +9797,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -10153,9 +10090,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10697,9 +10631,6 @@
       <c r="O61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -11141,9 +11072,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11685,9 +11613,6 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -11981,9 +11906,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12525,9 +12447,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12921,9 +12840,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -13217,9 +13133,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13761,9 +13674,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -14205,9 +14115,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14749,9 +14656,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -15045,9 +14949,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -15589,9 +15490,6 @@
       <c r="O90" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -16033,9 +15931,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16577,9 +16472,6 @@
       <c r="O96" t="n">
         <v>19</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.03957795938853511</v>
       </c>
@@ -17021,9 +16913,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17565,9 +17454,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -17861,9 +17747,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18405,9 +18288,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -18701,9 +18581,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19245,9 +19122,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -19541,9 +19415,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20085,9 +19956,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20529,9 +20397,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21073,9 +20938,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -21369,9 +21231,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -21913,9 +21772,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -22209,9 +22065,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -22753,9 +22606,6 @@
       <c r="O133" t="n">
         <v>2</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -23049,9 +22899,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -23593,9 +23440,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -23989,9 +23833,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -24137,9 +23978,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -24681,9 +24519,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -25225,9 +25060,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -25373,9 +25205,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -25917,9 +25746,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -26461,9 +26287,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -26609,9 +26432,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -27153,9 +26973,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -27697,9 +27514,6 @@
       <c r="O161" t="n">
         <v>17</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.03528572831253259</v>
       </c>
@@ -27845,9 +27659,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -28389,9 +28200,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -28933,9 +28741,6 @@
       <c r="O168" t="n">
         <v>68</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.1411429132501303</v>
       </c>
@@ -29081,9 +28886,6 @@
       <c r="O169" t="n">
         <v>11</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.2335947470912145</v>
       </c>
@@ -29773,9 +29575,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -30317,9 +30116,6 @@
       <c r="O176" t="n">
         <v>59</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.1224622335552601</v>
       </c>
@@ -30465,9 +30261,6 @@
       <c r="O177" t="n">
         <v>8</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.1698870887936106</v>
       </c>
@@ -31157,9 +30950,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -31701,9 +31491,6 @@
       <c r="O184" t="n">
         <v>20</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.04151262154415598</v>
       </c>
@@ -31849,9 +31636,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -32541,9 +32325,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -33085,9 +32866,6 @@
       <c r="O192" t="n">
         <v>22</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.04566388369857158</v>
       </c>
@@ -33233,9 +33011,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -33925,9 +33700,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -34469,9 +34241,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -34617,9 +34386,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -35161,9 +34927,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -35705,9 +35468,6 @@
       <c r="O207" t="n">
         <v>4</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -35853,9 +35613,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -36397,9 +36154,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -36941,9 +36695,6 @@
       <c r="O214" t="n">
         <v>4</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -37089,9 +36840,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -37633,9 +37381,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -38177,9 +37922,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -38325,9 +38067,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -39017,9 +38756,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -39561,9 +39297,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -39957,9 +39690,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -40105,9 +39835,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -40797,9 +40524,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -41341,9 +41065,6 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -41489,9 +41210,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -42033,9 +41751,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -42577,9 +42292,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -42725,9 +42437,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -43417,9 +43126,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -43961,9 +43667,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -44109,9 +43812,6 @@
       <c r="O255" t="n">
         <v>3</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.06291813029967276</v>
       </c>
@@ -44801,9 +44501,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -45345,9 +45042,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -45493,9 +45187,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -46037,9 +45728,6 @@
       <c r="O266" t="n">
         <v>1</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -46581,9 +46269,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -46729,9 +46414,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -47421,9 +47103,6 @@
       <c r="O274" t="n">
         <v>1</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -47965,9 +47644,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -48113,9 +47789,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -48657,9 +48330,6 @@
       <c r="O281" t="n">
         <v>2</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -49201,9 +48871,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -49349,9 +49016,6 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -50041,9 +49705,6 @@
       <c r="O289" t="n">
         <v>1</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -50585,9 +50246,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -50733,9 +50391,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -51277,9 +50932,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -51821,9 +51473,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -51969,9 +51618,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -52513,9 +52159,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -53057,9 +52700,6 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0</v>
       </c>
@@ -53205,9 +52845,6 @@
       <c r="O307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0</v>
       </c>
@@ -53897,9 +53534,6 @@
       <c r="O311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0</v>
       </c>
@@ -54441,9 +54075,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -54589,9 +54220,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -55281,9 +54909,6 @@
       <c r="O319" t="n">
         <v>0</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0</v>
       </c>
@@ -55825,9 +55450,6 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0</v>
       </c>
@@ -56221,9 +55843,6 @@
       <c r="O324" t="n">
         <v>1</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -56369,9 +55988,6 @@
       <c r="O325" t="n">
         <v>1</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -57061,9 +56677,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -57605,9 +57218,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -57753,9 +57363,6 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0</v>
       </c>
@@ -58445,9 +58052,6 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
@@ -58989,9 +58593,6 @@
       <c r="O340" t="n">
         <v>2</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -59137,9 +58738,6 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -59829,9 +59427,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -60373,9 +59968,6 @@
       <c r="O348" t="n">
         <v>2</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -60521,9 +60113,6 @@
       <c r="O349" t="n">
         <v>1</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -61213,9 +60802,6 @@
       <c r="O353" t="n">
         <v>1</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -61757,9 +61343,6 @@
       <c r="O356" t="n">
         <v>2</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -61905,9 +61488,6 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0</v>
       </c>
@@ -62597,9 +62177,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -63141,9 +62718,6 @@
       <c r="O364" t="n">
         <v>2</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -63289,9 +62863,6 @@
       <c r="O365" t="n">
         <v>0</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0</v>
       </c>
@@ -63833,9 +63404,6 @@
       <c r="O368" t="n">
         <v>0</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
@@ -64377,9 +63945,6 @@
       <c r="O371" t="n">
         <v>2</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -64525,9 +64090,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -65069,9 +64631,6 @@
       <c r="O375" t="n">
         <v>0</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
@@ -65613,9 +65172,6 @@
       <c r="O378" t="n">
         <v>1</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -65761,9 +65317,6 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0</v>
       </c>
@@ -66453,9 +66006,6 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
@@ -66997,9 +66547,6 @@
       <c r="O386" t="n">
         <v>0</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0</v>
       </c>
@@ -67145,9 +66692,6 @@
       <c r="O387" t="n">
         <v>0</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0</v>
       </c>
@@ -67689,9 +67233,6 @@
       <c r="O390" t="n">
         <v>0</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0</v>
       </c>
@@ -68233,9 +67774,6 @@
       <c r="O393" t="n">
         <v>2</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -68381,9 +67919,6 @@
       <c r="O394" t="n">
         <v>0</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0</v>
       </c>
@@ -68925,9 +68460,6 @@
       <c r="O397" t="n">
         <v>0</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0</v>
       </c>
@@ -69469,9 +69001,6 @@
       <c r="O400" t="n">
         <v>2</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -69617,9 +69146,6 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0</v>
       </c>
@@ -70161,9 +69687,6 @@
       <c r="O404" t="n">
         <v>1</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -70705,9 +70228,6 @@
       <c r="O407" t="n">
         <v>1</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -70851,9 +70371,6 @@
         <v>0</v>
       </c>
       <c r="O408" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q408" t="n">
         <v>0</v>
       </c>
       <c r="R408" t="n">
